--- a/docs/03_test/BlackBoxTest.xlsx
+++ b/docs/03_test/BlackBoxTest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\WEBアプリ開発演習\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3875560C-DF0E-4FA3-BBC8-8855254B355E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B141BC-C8C8-41EC-B62C-1DB227C947E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29085" yWindow="0" windowWidth="28620" windowHeight="15585" xr2:uid="{E01120ED-5E11-4FC7-A373-7E8728B03DDF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="997" firstSheet="1" activeTab="7" xr2:uid="{E01120ED-5E11-4FC7-A373-7E8728B03DDF}"/>
   </bookViews>
   <sheets>
     <sheet name="従業員登録ディシジョンテーブル" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,8 @@
     <sheet name="部署登録ディシジョンテーブル" sheetId="4" r:id="rId4"/>
     <sheet name="部署登録テスト記録" sheetId="5" r:id="rId5"/>
     <sheet name="部署登録テスト画像" sheetId="6" r:id="rId6"/>
+    <sheet name="社員一覧テスト" sheetId="7" r:id="rId7"/>
+    <sheet name="部署一覧テスト" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +50,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="25">
+  <futureMetadata name="XLRICHVALUE" count="29">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -224,8 +226,36 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="25"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="26"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="27"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="28"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="25">
+  <valueMetadata count="29">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -300,13 +330,25 @@
     </bk>
     <bk>
       <rc t="1" v="24"/>
+    </bk>
+    <bk>
+      <rc t="1" v="25"/>
+    </bk>
+    <bk>
+      <rc t="1" v="26"/>
+    </bk>
+    <bk>
+      <rc t="1" v="27"/>
+    </bk>
+    <bk>
+      <rc t="1" v="28"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="112">
   <si>
     <t>条件</t>
     <rPh sb="0" eb="2">
@@ -504,13 +546,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>テスト観点</t>
-    <rPh sb="3" eb="5">
-      <t>カンテン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>正常系</t>
     <rPh sb="0" eb="3">
       <t>セイジョウケイ</t>
@@ -796,13 +831,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>登録成功</t>
-    <rPh sb="0" eb="4">
-      <t>トウロクセイコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>途中から入力不可</t>
     <rPh sb="0" eb="2">
       <t>トチュウ</t>
@@ -1085,6 +1113,210 @@
   </si>
   <si>
     <t>（スペースのみ）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト結果</t>
+    <rPh sb="3" eb="5">
+      <t>ケッカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署名がNullの場合の表示</t>
+    <rPh sb="0" eb="3">
+      <t>ブショメイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日本語氏名の表示</t>
+    <rPh sb="0" eb="5">
+      <t>ニホンゴシメイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>英語氏名の表示</t>
+    <rPh sb="0" eb="2">
+      <t>エイゴ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シメイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールアドレスの表示</t>
+    <rPh sb="8" eb="10">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署名の表示</t>
+    <rPh sb="0" eb="3">
+      <t>ブショメイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雇用形態の表示</t>
+    <rPh sb="0" eb="4">
+      <t>コヨウケイタイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雇用形態がNullの場合の表示</t>
+    <rPh sb="0" eb="2">
+      <t>コヨウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケイタイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールドレス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DBと一致する氏名を表示</t>
+    <rPh sb="3" eb="5">
+      <t>イッチ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シメイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DBと一致するメールアドレスを表示</t>
+    <rPh sb="3" eb="5">
+      <t>イッチ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DBと一致する所属部署を表示</t>
+    <rPh sb="3" eb="5">
+      <t>イッチ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ショゾクブショ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DBと一致する雇用形態を表示</t>
+    <rPh sb="3" eb="5">
+      <t>イッチ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>コヨウケイタイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"-"を表示</t>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>用意されたDB</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>結果表示画面</t>
+    <rPh sb="0" eb="6">
+      <t>ケッカヒョウジガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力値が登録完了画面に表示される</t>
+    <rPh sb="0" eb="3">
+      <t>ニュウリョクチ</t>
+    </rPh>
+    <rPh sb="4" eb="10">
+      <t>トウロクカンリョウガメン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力値が登録完了画面に表示される</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト項目</t>
+    <rPh sb="3" eb="5">
+      <t>コウモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日本語部署名の表示</t>
+    <rPh sb="0" eb="6">
+      <t>ニホンゴブショメイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>英語部署名の表示</t>
+    <rPh sb="0" eb="5">
+      <t>エイゴブショメイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヒョウジ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1092,7 +1324,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1117,19 +1349,22 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="12">
@@ -1266,16 +1501,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1288,10 +1517,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1309,28 +1535,115 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
@@ -1342,85 +1655,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1482,7 +1729,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="25">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="29">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -1583,6 +1830,22 @@
     <v>24</v>
     <v>5</v>
   </rv>
+  <rv s="0">
+    <v>25</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>26</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>27</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>28</v>
+    <v>5</v>
+  </rv>
 </rvData>
 </file>
 
@@ -1622,6 +1885,10 @@
   <rel r:id="rId23"/>
   <rel r:id="rId24"/>
   <rel r:id="rId25"/>
+  <rel r:id="rId26"/>
+  <rel r:id="rId27"/>
+  <rel r:id="rId28"/>
+  <rel r:id="rId29"/>
 </richValueRels>
 </file>
 
@@ -1945,676 +2212,677 @@
   <dimension ref="A1:S22"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="27.58203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.58203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
+    <row r="1" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="18" t="s">
+    <row r="2" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="16">
         <v>1</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="16">
         <v>2</v>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="16">
         <v>3</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="16">
         <v>4</v>
       </c>
-      <c r="G2" s="20">
+      <c r="G2" s="16">
         <v>5</v>
       </c>
-      <c r="H2" s="20">
+      <c r="H2" s="16">
         <v>6</v>
       </c>
-      <c r="I2" s="20">
+      <c r="I2" s="16">
         <v>7</v>
       </c>
-      <c r="J2" s="20">
+      <c r="J2" s="16">
         <v>8</v>
       </c>
-      <c r="K2" s="20">
+      <c r="K2" s="16">
         <v>9</v>
       </c>
-      <c r="L2" s="20">
+      <c r="L2" s="16">
         <v>10</v>
       </c>
-      <c r="M2" s="20">
+      <c r="M2" s="16">
         <v>11</v>
       </c>
-      <c r="N2" s="20">
+      <c r="N2" s="16">
         <v>12</v>
       </c>
-      <c r="O2" s="20">
+      <c r="O2" s="16">
         <v>13</v>
       </c>
-      <c r="P2" s="20">
+      <c r="P2" s="16">
         <v>14</v>
       </c>
-      <c r="Q2" s="20">
+      <c r="Q2" s="16">
         <v>15</v>
       </c>
-      <c r="R2" s="20">
+      <c r="R2" s="16">
         <v>16</v>
       </c>
-      <c r="S2" s="21">
+      <c r="S2" s="17">
         <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="N3" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="O3" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="P3" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q3" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="R3" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="S3" s="24" t="s">
+      <c r="C3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="S3" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="32"/>
-      <c r="B4" s="25" t="s">
+      <c r="A4" s="19"/>
+      <c r="B4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="26"/>
-      <c r="S4" s="27"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="6"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="32"/>
-      <c r="B5" s="25" t="s">
+      <c r="A5" s="19"/>
+      <c r="B5" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="26"/>
-      <c r="Q5" s="26"/>
-      <c r="R5" s="26"/>
-      <c r="S5" s="27"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="6"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="32"/>
-      <c r="B6" s="25" t="s">
+      <c r="A6" s="19"/>
+      <c r="B6" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="26"/>
-      <c r="P6" s="26"/>
-      <c r="Q6" s="26"/>
-      <c r="R6" s="26"/>
-      <c r="S6" s="27"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="6"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="32"/>
-      <c r="B7" s="25" t="s">
+      <c r="A7" s="19"/>
+      <c r="B7" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
-      <c r="P7" s="26"/>
-      <c r="Q7" s="26"/>
-      <c r="R7" s="26"/>
-      <c r="S7" s="27"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="6"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="32"/>
-      <c r="B8" s="25" t="s">
+      <c r="A8" s="19"/>
+      <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="26"/>
-      <c r="S8" s="27"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="6"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="33"/>
-      <c r="B9" s="28" t="s">
+      <c r="A9" s="20"/>
+      <c r="B9" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="29"/>
-      <c r="S9" s="30"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="10"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="S10" s="5" t="s">
+      <c r="C10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="S10" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="35"/>
-      <c r="B11" s="7" t="s">
+      <c r="A11" s="19"/>
+      <c r="B11" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="9"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="6"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="35"/>
-      <c r="B12" s="7" t="s">
+      <c r="A12" s="19"/>
+      <c r="B12" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="9"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="6"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="35"/>
-      <c r="B13" s="7" t="s">
+      <c r="A13" s="19"/>
+      <c r="B13" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="9"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="6"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="35"/>
-      <c r="B14" s="7" t="s">
+      <c r="A14" s="19"/>
+      <c r="B14" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
-      <c r="S14" s="9"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="6"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="35"/>
-      <c r="B15" s="7" t="s">
+      <c r="A15" s="19"/>
+      <c r="B15" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
-      <c r="S15" s="9"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="6"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="35"/>
-      <c r="B16" s="7" t="s">
+      <c r="A16" s="19"/>
+      <c r="B16" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
-      <c r="S16" s="9"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="6"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="35"/>
-      <c r="B17" s="7" t="s">
+      <c r="A17" s="19"/>
+      <c r="B17" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
-      <c r="S17" s="9"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q17" s="5"/>
+      <c r="R17" s="5"/>
+      <c r="S17" s="6"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="36"/>
-      <c r="B18" s="11" t="s">
+      <c r="A18" s="20"/>
+      <c r="B18" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
-      <c r="O18" s="12"/>
-      <c r="P18" s="12"/>
-      <c r="Q18" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="R18" s="12"/>
-      <c r="S18" s="13"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="R18" s="9"/>
+      <c r="S18" s="10"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="34" t="s">
+      <c r="A19" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="S19" s="5"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="S19" s="3"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="36"/>
-      <c r="B20" s="11" t="s">
+      <c r="A20" s="20"/>
+      <c r="B20" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="H20" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="I20" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="J20" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="K20" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L20" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="M20" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="N20" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="O20" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="P20" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q20" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="R20" s="12"/>
-      <c r="S20" s="13" t="s">
+      <c r="C20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="N20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="O20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="P20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="R20" s="9"/>
+      <c r="S20" s="10" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="34" t="s">
+      <c r="A21" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="4"/>
-      <c r="S21" s="5" t="s">
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="36"/>
-      <c r="B22" s="11" t="s">
+      <c r="A22" s="20"/>
+      <c r="B22" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G22" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="I22" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="J22" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="K22" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L22" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="M22" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="N22" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="O22" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="P22" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q22" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="R22" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="S22" s="13"/>
+      <c r="C22" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="N22" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="O22" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="P22" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q22" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="R22" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="S22" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2633,774 +2901,775 @@
   <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="3.58203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.83203125" style="1" customWidth="1"/>
-    <col min="6" max="7" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="76.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="70.83203125" customWidth="1"/>
-    <col min="10" max="10" width="33.58203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.58203125" style="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" style="32" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.25" style="32" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.25" style="32" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.83203125" style="34" customWidth="1"/>
+    <col min="6" max="7" width="10.5" style="32" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="76.58203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="70.83203125" style="32" customWidth="1"/>
+    <col min="10" max="10" width="33.58203125" style="32" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" style="32" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.6640625" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="14"/>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="37" t="s">
+    <row r="1" spans="1:10" s="26" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="39"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="16" t="s">
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="25"/>
+    </row>
+    <row r="2" spans="1:10" s="26" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" s="30" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="31">
+        <v>1</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="J2" s="48" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="6">
-        <v>1</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="40" t="str">
+      <c r="D3" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="33" t="str">
         <f>"test"&amp;A3&amp;"@dogs.com"</f>
         <v>test1@dogs.com</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H3" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="I3" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="J3" s="42" t="s">
-        <v>75</v>
+      <c r="F3" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="I3" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="J3" s="35" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="6">
+      <c r="A4" s="31">
         <v>2</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="40" t="str">
+      <c r="C4" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="33" t="str">
         <f t="shared" ref="E4:E22" si="0">"test"&amp;A4&amp;"@dogs.com"</f>
         <v>test2@dogs.com</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H4" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="I4" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="J4" s="42" t="s">
-        <v>75</v>
+      <c r="F4" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="I4" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="J4" s="35" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="6">
+      <c r="A5" s="31">
         <v>3</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="40" t="str">
+      <c r="C5" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="33" t="str">
         <f t="shared" si="0"/>
         <v>test3@dogs.com</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H5" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="I5" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="J5" s="42" t="s">
-        <v>75</v>
+      <c r="F5" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="J5" s="35" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="6">
+      <c r="A6" s="31">
         <v>4</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="40" t="str">
+      <c r="C6" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="33" t="str">
         <f t="shared" si="0"/>
         <v>test4@dogs.com</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H6" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="I6" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="J6" s="42" t="s">
-        <v>75</v>
+      <c r="F6" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="I6" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="J6" s="35" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="6">
+      <c r="A7" s="31">
         <v>5</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="40" t="str">
+      <c r="C7" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="33" t="str">
         <f t="shared" si="0"/>
         <v>test5@dogs.com</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H7" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="I7" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="J7" s="42" t="s">
-        <v>75</v>
+      <c r="F7" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="I7" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="J7" s="35" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="6">
+      <c r="A8" s="31">
         <v>6</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="40" t="str">
+      <c r="C8" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="33" t="str">
         <f t="shared" si="0"/>
         <v>test6@dogs.com</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H8" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="I8" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="J8" s="42" t="s">
-        <v>75</v>
+      <c r="F8" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" s="35" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="6">
+      <c r="A9" s="31">
         <v>7</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" s="40" t="str">
+      <c r="C9" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="33" t="str">
         <f t="shared" si="0"/>
         <v>test7@dogs.com</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H9" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="I9" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="J9" s="42" t="s">
-        <v>75</v>
+      <c r="F9" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" s="35" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="6">
+      <c r="A10" s="31">
         <v>8</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="I10" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="J10" s="35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="31">
+        <v>9</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="J11" s="35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="31">
+        <v>10</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" s="43" t="s">
-        <v>71</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H10" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="I10" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="J10" s="42" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="6">
-        <v>9</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H11" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="I11" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="J11" s="42" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="6">
-        <v>10</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="40" t="str">
+      <c r="D12" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="33" t="str">
         <f>"test"&amp;A12&amp;".dogs.com"</f>
         <v>test10.dogs.com</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H12" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="I12" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="J12" s="42" t="s">
-        <v>75</v>
+      <c r="F12" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="H12" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="I12" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="J12" s="35" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="6">
+      <c r="A13" s="31">
         <v>11</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="I13" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="J13" s="35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="31">
+        <v>12</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E13" s="41" t="s">
-        <v>73</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H13" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="I13" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="J13" s="42" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="6">
-        <v>12</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14" s="40" t="str">
+      <c r="D14" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="33" t="str">
         <f>"テスト"&amp;A14&amp;"@dogs.com"</f>
         <v>テスト12@dogs.com</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H14" s="41" t="s">
+      <c r="F14" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="I14" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="J14" s="35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="31">
+        <v>13</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="H15" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="I15" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="J15" s="35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="31">
+        <v>14</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="I14" s="41" t="s">
+      <c r="I16" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="J14" s="42" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="6">
-        <v>13</v>
-      </c>
-      <c r="B15" s="7" t="s">
+      <c r="J16" s="35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="31">
+        <v>15</v>
+      </c>
+      <c r="B17" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C17" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="H17" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="I17" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="J17" s="35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="31">
+        <v>16</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H15" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="I15" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="J15" s="42" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="6">
-        <v>14</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E16" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H16" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="I16" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="J16" s="42" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="6">
-        <v>15</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H17" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="I17" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="J17" s="42" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="6">
-        <v>16</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18" s="40" t="str">
+      <c r="D18" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="33" t="str">
         <f t="shared" si="0"/>
         <v>test16@dogs.com</v>
       </c>
-      <c r="F18" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H18" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="I18" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="J18" s="42" t="s">
-        <v>75</v>
+      <c r="F18" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="H18" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="I18" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="J18" s="35" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="6">
+      <c r="A19" s="31">
         <v>17</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E19" s="40" t="str">
+      <c r="C19" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="33" t="str">
         <f t="shared" si="0"/>
         <v>test17@dogs.com</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="G19" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="H19" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="I19" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="J19" s="42" t="s">
-        <v>75</v>
+      <c r="H19" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="I19" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="J19" s="35" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="6">
+      <c r="A20" s="31">
         <v>18</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E20" s="40" t="str">
+      <c r="D20" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" s="33" t="str">
         <f t="shared" si="0"/>
         <v>test18@dogs.com</v>
       </c>
-      <c r="F20" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H20" s="41" t="s">
-        <v>68</v>
-      </c>
-      <c r="I20" s="41" t="s">
-        <v>68</v>
-      </c>
-      <c r="J20" s="42" t="s">
-        <v>76</v>
+      <c r="F20" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="H20" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="I20" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="J20" s="35" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="6">
+      <c r="A21" s="31">
         <v>19</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="7" t="s">
+      <c r="B21" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E21" s="40" t="str">
+      <c r="D21" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="33" t="str">
         <f t="shared" si="0"/>
         <v>test19@dogs.com</v>
       </c>
-      <c r="F21" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H21" s="41" t="s">
-        <v>68</v>
-      </c>
-      <c r="I21" s="41" t="s">
-        <v>68</v>
-      </c>
-      <c r="J21" s="42" t="s">
-        <v>76</v>
+      <c r="F21" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="H21" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="I21" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="J21" s="35" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="10">
+      <c r="A22" s="37">
         <v>20</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="11" t="s">
+      <c r="B22" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E22" s="44" t="str">
+      <c r="E22" s="39" t="str">
         <f t="shared" si="0"/>
         <v>test20@dogs.com</v>
       </c>
-      <c r="F22" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="H22" s="45" t="s">
-        <v>68</v>
-      </c>
-      <c r="I22" s="45" t="s">
-        <v>68</v>
-      </c>
-      <c r="J22" s="46" t="s">
-        <v>76</v>
+      <c r="F22" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="H22" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="I22" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="J22" s="41" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="E23" s="2"/>
+      <c r="E23" s="42"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="E24" s="2"/>
+      <c r="E24" s="42"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="E25" s="2"/>
+      <c r="E25" s="42"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="E26" s="2"/>
+      <c r="E26" s="42"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="E27" s="2"/>
+      <c r="E27" s="42"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="E28" s="2"/>
+      <c r="E28" s="42"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="E29" s="2"/>
+      <c r="E29" s="42"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="E30" s="2"/>
+      <c r="E30" s="42"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="E31" s="2"/>
+      <c r="E31" s="42"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="E32" s="2"/>
+      <c r="E32" s="42"/>
     </row>
     <row r="33" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E33" s="2"/>
+      <c r="E33" s="42"/>
     </row>
     <row r="34" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E34" s="2"/>
+      <c r="E34" s="42"/>
     </row>
     <row r="35" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E35" s="2"/>
+      <c r="E35" s="42"/>
     </row>
     <row r="36" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E36" s="2"/>
+      <c r="E36" s="42"/>
     </row>
     <row r="37" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E37" s="2"/>
+      <c r="E37" s="42"/>
     </row>
     <row r="38" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E38" s="2"/>
+      <c r="E38" s="42"/>
     </row>
     <row r="39" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E39" s="2"/>
+      <c r="E39" s="42"/>
     </row>
     <row r="40" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E40" s="2"/>
+      <c r="E40" s="42"/>
     </row>
     <row r="41" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E41" s="2"/>
+      <c r="E41" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3419,153 +3688,153 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E23A5BC1-1A2C-4810-A079-76D1C51642AA}">
-  <dimension ref="B1:C18"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="3" max="3" width="43.9140625" customWidth="1"/>
+    <col min="2" max="2" width="43.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" ht="23.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" t="s">
+    <row r="1" spans="1:2" ht="23.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="C1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="2:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2">
+      <c r="B1" s="43" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="C2" t="e" vm="1">
+      <c r="B2" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="3" spans="2:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3">
+    <row r="3" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="C3" t="e" vm="2">
+      <c r="B3" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="2:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4">
+    <row r="4" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="C4" t="e" vm="3">
+      <c r="B4" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5">
+    <row r="5" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="C5" t="e" vm="4">
+      <c r="B5" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6" spans="2:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6">
+    <row r="6" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="C6" t="e" vm="5">
+      <c r="B6" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="7" spans="2:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7">
+    <row r="7" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="C7" t="e" vm="6">
+      <c r="B7" t="e" vm="6">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="8" spans="2:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8">
+    <row r="8" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="C8" t="e" vm="7">
+      <c r="B8" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9">
+    <row r="9" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="C9" t="e" vm="8">
+      <c r="B9" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="2:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10">
+    <row r="10" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="C10" t="e" vm="9">
+      <c r="B10" t="e" vm="9">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11">
+    <row r="11" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="C11" t="e" vm="10">
+      <c r="B11" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="12" spans="2:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12">
+    <row r="12" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="C12" t="e" vm="11">
+      <c r="B12" t="e" vm="11">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="13" spans="2:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13">
+    <row r="13" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="C13" t="e" vm="12">
+      <c r="B13" t="e" vm="12">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="14" spans="2:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14">
+    <row r="14" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="C14" t="e" vm="13">
+      <c r="B14" t="e" vm="13">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="15" spans="2:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15">
+    <row r="15" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="C15" t="e" vm="14">
+      <c r="B15" t="e" vm="14">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="16" spans="2:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16">
+    <row r="16" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="C16" t="e" vm="15">
+      <c r="B16" t="e" vm="15">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17">
+    <row r="17" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="C17" t="e" vm="16">
+      <c r="B17" t="e" vm="16">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="18" spans="2:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18">
+    <row r="18" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="C18" t="e" vm="17">
+      <c r="B18" t="e" vm="17">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -3577,324 +3846,190 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B50E3B-0291-4389-BEDF-41D323EABE8C}">
-  <dimension ref="A1:T14"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="27.58203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="27.58203125" style="32" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.6640625" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
+    <row r="1" spans="1:20" s="26" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="26" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="18" t="s">
+    <row r="2" spans="1:20" s="26" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="46">
         <v>1</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="46">
         <v>2</v>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="46">
         <v>3</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="46">
         <v>4</v>
       </c>
-      <c r="G2" s="20">
+      <c r="G2" s="46">
         <v>5</v>
       </c>
-      <c r="H2" s="20">
+      <c r="H2" s="46">
         <v>6</v>
       </c>
-      <c r="I2" s="20">
+      <c r="I2" s="46">
         <v>7</v>
       </c>
-      <c r="J2" s="20">
+      <c r="J2" s="46">
         <v>8</v>
       </c>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="47"/>
+      <c r="S2" s="47"/>
+      <c r="T2" s="47"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="48" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="51"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="51"/>
+      <c r="T3" s="51"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="31"/>
+      <c r="B4" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="51"/>
+      <c r="O4" s="51"/>
+      <c r="P4" s="51"/>
+      <c r="Q4" s="51"/>
+      <c r="R4" s="51"/>
+      <c r="S4" s="51"/>
+      <c r="T4" s="51"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="31"/>
+      <c r="B5" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="50"/>
-      <c r="B4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="6"/>
-      <c r="B5" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="42"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
+      <c r="E5" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="35"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="6"/>
-      <c r="B6" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
+      <c r="A6" s="31"/>
+      <c r="B6" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="51"/>
+      <c r="J6" s="35"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="6"/>
-      <c r="B7" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
+      <c r="A7" s="31"/>
+      <c r="B7" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="35"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="6"/>
-      <c r="B8" s="25" t="s">
+      <c r="A8" s="31"/>
+      <c r="B8" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="7"/>
-      <c r="J8" s="42"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
+      <c r="H8" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="35"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="6"/>
-      <c r="B9" s="25" t="s">
+      <c r="A9" s="31"/>
+      <c r="B9" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="42"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
+      <c r="I9" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="35"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="10"/>
-      <c r="B10" s="28" t="s">
+      <c r="A10" s="37"/>
+      <c r="B10" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="53" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
+      <c r="K11" s="51"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
+      <c r="L12" s="51"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
+      <c r="M13" s="51"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -3907,325 +4042,288 @@
   <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="51.75" customWidth="1"/>
-    <col min="5" max="5" width="53.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="54.1640625" customWidth="1"/>
-    <col min="7" max="7" width="33.58203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" style="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="32" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.25" style="32" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="51.75" style="32" customWidth="1"/>
+    <col min="5" max="5" width="53.83203125" style="34" customWidth="1"/>
+    <col min="6" max="6" width="54.1640625" style="32" customWidth="1"/>
+    <col min="7" max="7" width="33.58203125" style="32" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" style="32" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.6640625" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="14"/>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="51" t="s">
+    <row r="1" spans="1:7" s="26" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="38"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="39"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="16" t="s">
+      <c r="E1" s="24"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="25"/>
+    </row>
+    <row r="2" spans="1:7" s="26" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="17" t="s">
+      <c r="B2" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="E2" s="47" t="s">
+      <c r="D2" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="G2" s="48" t="s">
-        <v>70</v>
+      <c r="F2" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="6">
+      <c r="A3" s="31">
         <v>1</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" s="7" t="s">
+      <c r="B3" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="G3" s="35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="31">
+        <v>2</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="41" t="s">
+      <c r="D4" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="G4" s="35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="31">
+        <v>3</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="31">
+        <v>4</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G3" s="42" t="s">
+      <c r="E6" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="G6" s="35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="31">
+        <v>5</v>
+      </c>
+      <c r="B7" s="32" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="6">
-        <v>2</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="41" t="s">
-        <v>85</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G4" s="42" t="s">
+      <c r="C7" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="31">
+        <v>6</v>
+      </c>
+      <c r="B8" s="32" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="6">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="C8" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="G8" s="35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="31">
+        <v>7</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="D5" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G5" s="42" t="s">
+      <c r="D9" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="E9" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="G9" s="35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="37">
+        <v>8</v>
+      </c>
+      <c r="B10" s="38" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="6">
-        <v>4</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" s="41" t="s">
-        <v>88</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G6" s="42" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="6">
-        <v>5</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" s="41" t="s">
-        <v>91</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G7" s="42" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="6">
-        <v>6</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="G8" s="42" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="6">
-        <v>7</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" s="7" t="s">
+      <c r="C10" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="41" t="s">
-        <v>92</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="G9" s="42" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="10">
-        <v>8</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="G10" s="46" t="s">
-        <v>75</v>
+      <c r="F10" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="G10" s="41" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="7"/>
+      <c r="F11" s="34"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="7"/>
+      <c r="F12" s="34"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="7"/>
+      <c r="F13" s="34"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="7"/>
+      <c r="F14" s="34"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="7"/>
+      <c r="F15" s="34"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="7"/>
-      <c r="E16"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="7"/>
-      <c r="E17"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="7"/>
-      <c r="E18"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="7"/>
-      <c r="E19"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="7"/>
-      <c r="E20"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="7"/>
-      <c r="E21"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="7"/>
-      <c r="E22"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="7"/>
-      <c r="E23"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E24"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E25"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E26"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E27"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E28"/>
+      <c r="E16" s="32"/>
+    </row>
+    <row r="17" spans="5:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="E17" s="32"/>
+    </row>
+    <row r="18" spans="5:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="E18" s="32"/>
+    </row>
+    <row r="19" spans="5:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="E19" s="32"/>
+    </row>
+    <row r="20" spans="5:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="E20" s="32"/>
+    </row>
+    <row r="21" spans="5:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="E21" s="32"/>
+    </row>
+    <row r="22" spans="5:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="E22" s="32"/>
+    </row>
+    <row r="23" spans="5:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="E23" s="32"/>
+    </row>
+    <row r="24" spans="5:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="E24" s="32"/>
+    </row>
+    <row r="25" spans="5:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="E25" s="32"/>
+    </row>
+    <row r="26" spans="5:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="E26" s="32"/>
+    </row>
+    <row r="27" spans="5:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="E27" s="32"/>
+    </row>
+    <row r="28" spans="5:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="E28" s="32"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -4243,11 +4341,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
+      <c r="A1" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="B1" t="s">
-        <v>74</v>
+      <c r="B1" s="43" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="130.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -4311,6 +4409,261 @@
         <v>8</v>
       </c>
       <c r="B9" t="e" vm="25">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C935F76-C443-4762-9BD4-8347B550B6A9}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="12.4140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.08203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.58203125" customWidth="1"/>
+    <col min="5" max="5" width="38.08203125" customWidth="1"/>
+    <col min="7" max="7" width="5.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="54" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="55" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="55" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="55" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="55" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="7">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="D10" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="54" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="136" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D11" s="7" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E11" s="12" t="e" vm="27">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B31F7E87-04EC-4A6F-8E57-6DCCFE4577DD}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="55.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="54" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="D5" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="E5" s="54" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="179.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D6" s="7" t="e" vm="28">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E6" s="12" t="e" vm="29">
         <v>#VALUE!</v>
       </c>
     </row>

--- a/docs/03_test/BlackBoxTest.xlsx
+++ b/docs/03_test/BlackBoxTest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\WEBアプリ開発演習\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B141BC-C8C8-41EC-B62C-1DB227C947E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{605CB2ED-1162-4EC4-9AA7-FB54F4F77918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="997" firstSheet="1" activeTab="7" xr2:uid="{E01120ED-5E11-4FC7-A373-7E8728B03DDF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="997" xr2:uid="{E01120ED-5E11-4FC7-A373-7E8728B03DDF}"/>
   </bookViews>
   <sheets>
     <sheet name="従業員登録ディシジョンテーブル" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="29">
+  <futureMetadata name="XLRICHVALUE" count="33">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -254,8 +254,36 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="29"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="30"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="31"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="32"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="29">
+  <valueMetadata count="33">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -342,13 +370,25 @@
     </bk>
     <bk>
       <rc t="1" v="28"/>
+    </bk>
+    <bk>
+      <rc t="1" v="29"/>
+    </bk>
+    <bk>
+      <rc t="1" v="30"/>
+    </bk>
+    <bk>
+      <rc t="1" v="31"/>
+    </bk>
+    <bk>
+      <rc t="1" v="32"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="118">
   <si>
     <t>条件</t>
     <rPh sb="0" eb="2">
@@ -1315,6 +1355,66 @@
       <t>エイゴブショメイ</t>
     </rPh>
     <rPh sb="6" eb="8">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>確認画面でアラートが表示される。入力値が登録完了画面に表示される。</t>
+    <rPh sb="0" eb="4">
+      <t>カクニンガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>確認画面でアラートが表示される。入力値が登録完了画面に表示される。</t>
+    <rPh sb="0" eb="6">
+      <t>ガメンセンイセイコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>結果画面１</t>
+    <rPh sb="0" eb="4">
+      <t>ケッカガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>結果画面２</t>
+    <rPh sb="0" eb="4">
+      <t>ケッカガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>所属部署、雇用形態</t>
+    <rPh sb="0" eb="4">
+      <t>ショゾクブショ</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>コヨウケイタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>両項目で未選択の場合、アラートが正しく表示されるか</t>
+    <rPh sb="0" eb="3">
+      <t>リョウコウモク</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ミセンタク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -1501,7 +1601,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1556,6 +1656,54 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1565,110 +1713,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1729,7 +1775,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="29">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="33">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -1846,6 +1892,22 @@
     <v>28</v>
     <v>5</v>
   </rv>
+  <rv s="0">
+    <v>29</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>30</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>31</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>32</v>
+    <v>5</v>
+  </rv>
 </rvData>
 </file>
 
@@ -1889,6 +1951,10 @@
   <rel r:id="rId27"/>
   <rel r:id="rId28"/>
   <rel r:id="rId29"/>
+  <rel r:id="rId30"/>
+  <rel r:id="rId31"/>
+  <rel r:id="rId32"/>
+  <rel r:id="rId33"/>
 </richValueRels>
 </file>
 
@@ -2281,7 +2347,7 @@
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="34" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -2328,7 +2394,7 @@
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="19"/>
+      <c r="A4" s="35"/>
       <c r="B4" t="s">
         <v>5</v>
       </c>
@@ -2353,7 +2419,7 @@
       <c r="S4" s="6"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="19"/>
+      <c r="A5" s="35"/>
       <c r="B5" t="s">
         <v>6</v>
       </c>
@@ -2378,7 +2444,7 @@
       <c r="S5" s="6"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="19"/>
+      <c r="A6" s="35"/>
       <c r="B6" t="s">
         <v>4</v>
       </c>
@@ -2403,7 +2469,7 @@
       <c r="S6" s="6"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="19"/>
+      <c r="A7" s="35"/>
       <c r="B7" t="s">
         <v>14</v>
       </c>
@@ -2428,7 +2494,7 @@
       <c r="S7" s="6"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="19"/>
+      <c r="A8" s="35"/>
       <c r="B8" t="s">
         <v>8</v>
       </c>
@@ -2453,7 +2519,7 @@
       <c r="S8" s="6"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="20"/>
+      <c r="A9" s="36"/>
       <c r="B9" s="8" t="s">
         <v>7</v>
       </c>
@@ -2478,7 +2544,7 @@
       <c r="S9" s="10"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="34" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -2521,7 +2587,7 @@
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="19"/>
+      <c r="A11" s="35"/>
       <c r="B11" t="s">
         <v>11</v>
       </c>
@@ -2546,7 +2612,7 @@
       <c r="S11" s="6"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="19"/>
+      <c r="A12" s="35"/>
       <c r="B12" t="s">
         <v>12</v>
       </c>
@@ -2571,7 +2637,7 @@
       <c r="S12" s="6"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="19"/>
+      <c r="A13" s="35"/>
       <c r="B13" t="s">
         <v>13</v>
       </c>
@@ -2596,7 +2662,7 @@
       <c r="S13" s="6"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="19"/>
+      <c r="A14" s="35"/>
       <c r="B14" t="s">
         <v>15</v>
       </c>
@@ -2621,7 +2687,7 @@
       <c r="S14" s="6"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="19"/>
+      <c r="A15" s="35"/>
       <c r="B15" t="s">
         <v>16</v>
       </c>
@@ -2646,7 +2712,7 @@
       <c r="S15" s="6"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="19"/>
+      <c r="A16" s="35"/>
       <c r="B16" t="s">
         <v>14</v>
       </c>
@@ -2671,7 +2737,7 @@
       <c r="S16" s="6"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="19"/>
+      <c r="A17" s="35"/>
       <c r="B17" t="s">
         <v>8</v>
       </c>
@@ -2696,7 +2762,7 @@
       <c r="S17" s="6"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="20"/>
+      <c r="A18" s="36"/>
       <c r="B18" s="8" t="s">
         <v>7</v>
       </c>
@@ -2721,7 +2787,7 @@
       <c r="S18" s="10"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="34" t="s">
         <v>20</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -2748,7 +2814,7 @@
       <c r="S19" s="3"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="20"/>
+      <c r="A20" s="36"/>
       <c r="B20" s="8" t="s">
         <v>19</v>
       </c>
@@ -2803,7 +2869,7 @@
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="34" t="s">
         <v>17</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -2830,7 +2896,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="20"/>
+      <c r="A22" s="36"/>
       <c r="B22" s="8" t="s">
         <v>19</v>
       </c>
@@ -2898,778 +2964,810 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D12ED403-6FF0-4833-B4C5-5CA3D63780DB}">
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="3.58203125" style="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" style="32" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.25" style="32" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.25" style="32" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.83203125" style="34" customWidth="1"/>
-    <col min="6" max="7" width="10.5" style="32" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="76.58203125" style="34" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="70.83203125" style="32" customWidth="1"/>
-    <col min="10" max="10" width="33.58203125" style="32" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" style="32" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.6640625" style="32"/>
+    <col min="1" max="1" width="3.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.83203125" style="27" customWidth="1"/>
+    <col min="6" max="7" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="76.58203125" style="27" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="70.83203125" customWidth="1"/>
+    <col min="10" max="10" width="33.58203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="26" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="22"/>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="21" t="s">
+    <row r="1" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="25"/>
-    </row>
-    <row r="2" spans="1:10" s="26" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="27" t="s">
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="21"/>
+    </row>
+    <row r="2" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="28" t="s">
+      <c r="F2" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="G2" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="29" t="s">
+      <c r="H2" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="28" t="s">
+      <c r="I2" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="30" t="s">
+      <c r="J2" s="25" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="31">
+      <c r="A3" s="4">
         <v>1</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="33" t="str">
+      <c r="E3" s="26" t="str">
         <f>"test"&amp;A3&amp;"@dogs.com"</f>
         <v>test1@dogs.com</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="F3" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" t="s">
         <v>57</v>
       </c>
-      <c r="H3" s="34" t="s">
+      <c r="H3" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="I3" s="34" t="s">
+      <c r="I3" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="J3" s="35" t="s">
+      <c r="J3" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="31">
+      <c r="A4" s="4">
         <v>2</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="33" t="str">
-        <f t="shared" ref="E4:E22" si="0">"test"&amp;A4&amp;"@dogs.com"</f>
+      <c r="E4" s="26" t="str">
+        <f t="shared" ref="E4:E19" si="0">"test"&amp;A4&amp;"@dogs.com"</f>
         <v>test2@dogs.com</v>
       </c>
-      <c r="F4" s="32" t="s">
+      <c r="F4" t="s">
         <v>53</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="34" t="s">
+      <c r="H4" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="I4" s="34" t="s">
+      <c r="I4" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="J4" s="35" t="s">
+      <c r="J4" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="31">
+      <c r="A5" s="4">
         <v>3</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="33" t="str">
+      <c r="E5" s="26" t="str">
         <f t="shared" si="0"/>
         <v>test3@dogs.com</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="G5" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="34" t="s">
+      <c r="H5" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="I5" s="34" t="s">
+      <c r="I5" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="J5" s="35" t="s">
+      <c r="J5" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="31">
+      <c r="A6" s="4">
         <v>4</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="33" t="str">
+      <c r="E6" s="26" t="str">
         <f t="shared" si="0"/>
         <v>test4@dogs.com</v>
       </c>
-      <c r="F6" s="32" t="s">
+      <c r="F6" t="s">
         <v>53</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G6" t="s">
         <v>57</v>
       </c>
-      <c r="H6" s="34" t="s">
+      <c r="H6" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="I6" s="34" t="s">
+      <c r="I6" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="J6" s="35" t="s">
+      <c r="J6" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="31">
+      <c r="A7" s="4">
         <v>5</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" t="s">
         <v>60</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="33" t="str">
+      <c r="E7" s="26" t="str">
         <f t="shared" si="0"/>
         <v>test5@dogs.com</v>
       </c>
-      <c r="F7" s="32" t="s">
+      <c r="F7" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="32" t="s">
+      <c r="G7" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="34" t="s">
+      <c r="H7" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="I7" s="34" t="s">
+      <c r="I7" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="J7" s="35" t="s">
+      <c r="J7" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="31">
+      <c r="A8" s="4">
         <v>6</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="33" t="str">
+      <c r="E8" s="26" t="str">
         <f t="shared" si="0"/>
         <v>test6@dogs.com</v>
       </c>
-      <c r="F8" s="32" t="s">
+      <c r="F8" t="s">
         <v>53</v>
       </c>
-      <c r="G8" s="32" t="s">
+      <c r="G8" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="34" t="s">
+      <c r="H8" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="I8" s="34" t="s">
+      <c r="I8" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="J8" s="35" t="s">
+      <c r="J8" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="31">
+      <c r="A9" s="4">
         <v>7</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="33" t="str">
+      <c r="E9" s="26" t="str">
         <f t="shared" si="0"/>
         <v>test7@dogs.com</v>
       </c>
-      <c r="F9" s="32" t="s">
+      <c r="F9" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="32" t="s">
+      <c r="G9" t="s">
         <v>57</v>
       </c>
-      <c r="H9" s="34" t="s">
+      <c r="H9" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="I9" s="34" t="s">
+      <c r="I9" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="J9" s="35" t="s">
+      <c r="J9" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="31">
+      <c r="A10" s="4">
         <v>8</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="36" t="s">
+      <c r="E10" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="F10" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="32" t="s">
+      <c r="G10" t="s">
         <v>57</v>
       </c>
-      <c r="H10" s="34" t="s">
+      <c r="H10" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="I10" s="34" t="s">
+      <c r="I10" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="J10" s="35" t="s">
+      <c r="J10" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="31">
+      <c r="A11" s="4">
         <v>9</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="B11" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="36" t="s">
+      <c r="E11" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="F11" s="32" t="s">
+      <c r="F11" t="s">
         <v>53</v>
       </c>
-      <c r="G11" s="32" t="s">
+      <c r="G11" t="s">
         <v>57</v>
       </c>
-      <c r="H11" s="34" t="s">
+      <c r="H11" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="I11" s="34" t="s">
+      <c r="I11" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="J11" s="35" t="s">
+      <c r="J11" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="31">
+      <c r="A12" s="4">
         <v>10</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="33" t="str">
+      <c r="E12" s="26" t="str">
         <f>"test"&amp;A12&amp;".dogs.com"</f>
         <v>test10.dogs.com</v>
       </c>
-      <c r="F12" s="32" t="s">
+      <c r="F12" t="s">
         <v>53</v>
       </c>
-      <c r="G12" s="32" t="s">
+      <c r="G12" t="s">
         <v>57</v>
       </c>
-      <c r="H12" s="34" t="s">
+      <c r="H12" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="I12" s="34" t="s">
+      <c r="I12" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="J12" s="35" t="s">
+      <c r="J12" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="31">
+      <c r="A13" s="4">
         <v>11</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="B13" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="34" t="s">
+      <c r="E13" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="F13" s="32" t="s">
+      <c r="F13" t="s">
         <v>53</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="G13" t="s">
         <v>57</v>
       </c>
-      <c r="H13" s="34" t="s">
+      <c r="H13" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="I13" s="34" t="s">
+      <c r="I13" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="J13" s="35" t="s">
+      <c r="J13" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="31">
+      <c r="A14" s="4">
         <v>12</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="33" t="str">
+      <c r="E14" s="26" t="str">
         <f>"テスト"&amp;A14&amp;"@dogs.com"</f>
         <v>テスト12@dogs.com</v>
       </c>
-      <c r="F14" s="32" t="s">
+      <c r="F14" t="s">
         <v>53</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" t="s">
         <v>57</v>
       </c>
-      <c r="H14" s="34" t="s">
+      <c r="H14" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="I14" s="34" t="s">
+      <c r="I14" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="J14" s="35" t="s">
+      <c r="J14" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="31">
+      <c r="A15" s="4">
         <v>13</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="33" t="s">
+      <c r="E15" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="F15" s="32" t="s">
+      <c r="F15" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="32" t="s">
+      <c r="G15" t="s">
         <v>57</v>
       </c>
-      <c r="H15" s="34" t="s">
+      <c r="H15" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="I15" s="34" t="s">
+      <c r="I15" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="J15" s="35" t="s">
+      <c r="J15" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="31">
+      <c r="A16" s="4">
         <v>14</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B16" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="33" t="s">
+      <c r="E16" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="32" t="s">
+      <c r="F16" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="32" t="s">
+      <c r="G16" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="34" t="s">
+      <c r="H16" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="I16" s="34" t="s">
+      <c r="I16" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="J16" s="35" t="s">
+      <c r="J16" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="31">
+      <c r="A17" s="4">
         <v>15</v>
       </c>
-      <c r="B17" s="32" t="s">
+      <c r="B17" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C17" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="33" t="s">
+      <c r="E17" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="32" t="s">
+      <c r="F17" t="s">
         <v>53</v>
       </c>
-      <c r="G17" s="32" t="s">
+      <c r="G17" t="s">
         <v>57</v>
       </c>
-      <c r="H17" s="34" t="s">
+      <c r="H17" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="I17" s="34" t="s">
+      <c r="I17" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="J17" s="35" t="s">
+      <c r="J17" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="31">
+      <c r="A18" s="4">
         <v>16</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="B18" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="32" t="s">
+      <c r="C18" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="33" t="str">
+      <c r="E18" s="26" t="str">
         <f t="shared" si="0"/>
         <v>test16@dogs.com</v>
       </c>
-      <c r="F18" s="32" t="s">
+      <c r="F18" t="s">
         <v>54</v>
       </c>
-      <c r="G18" s="32" t="s">
+      <c r="G18" t="s">
         <v>57</v>
       </c>
-      <c r="H18" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="I18" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="J18" s="35" t="s">
+      <c r="H18" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="I18" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="J18" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="31">
+      <c r="A19" s="4">
         <v>17</v>
       </c>
-      <c r="B19" s="32" t="s">
+      <c r="B19" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="32" t="s">
+      <c r="C19" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="33" t="str">
+      <c r="E19" s="26" t="str">
         <f t="shared" si="0"/>
         <v>test17@dogs.com</v>
       </c>
-      <c r="F19" s="32" t="s">
+      <c r="F19" t="s">
         <v>53</v>
       </c>
-      <c r="G19" s="32" t="s">
+      <c r="G19" t="s">
         <v>54</v>
       </c>
-      <c r="H19" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="I19" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="J19" s="35" t="s">
+      <c r="H19" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="I19" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="J19" s="11" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="31">
+    <row r="20" spans="1:10" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="4">
         <v>18</v>
       </c>
-      <c r="B20" s="32" t="s">
+      <c r="B20" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" s="26" t="str">
+        <f t="shared" ref="E20:E23" si="1">"test"&amp;A20&amp;"@dogs.com"</f>
+        <v>test18@dogs.com</v>
+      </c>
+      <c r="F20" t="s">
+        <v>54</v>
+      </c>
+      <c r="G20" t="s">
+        <v>54</v>
+      </c>
+      <c r="H20" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="I20" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="4">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C21" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D21" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="33" t="str">
-        <f t="shared" si="0"/>
-        <v>test18@dogs.com</v>
-      </c>
-      <c r="F20" s="32" t="s">
+      <c r="E21" s="26" t="str">
+        <f t="shared" si="1"/>
+        <v>test19@dogs.com</v>
+      </c>
+      <c r="F21" t="s">
         <v>53</v>
       </c>
-      <c r="G20" s="32" t="s">
+      <c r="G21" t="s">
         <v>57</v>
       </c>
-      <c r="H20" s="34" t="s">
+      <c r="H21" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="I20" s="34" t="s">
+      <c r="I21" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="J20" s="35" t="s">
+      <c r="J21" s="11" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="31">
-        <v>19</v>
-      </c>
-      <c r="B21" s="32" t="s">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="4">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="32" t="s">
+      <c r="C22" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D22" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="33" t="str">
-        <f t="shared" si="0"/>
-        <v>test19@dogs.com</v>
-      </c>
-      <c r="F21" s="32" t="s">
+      <c r="E22" s="26" t="str">
+        <f t="shared" si="1"/>
+        <v>test20@dogs.com</v>
+      </c>
+      <c r="F22" t="s">
         <v>53</v>
       </c>
-      <c r="G21" s="32" t="s">
+      <c r="G22" t="s">
         <v>57</v>
       </c>
-      <c r="H21" s="34" t="s">
+      <c r="H22" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="I21" s="34" t="s">
+      <c r="I22" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="J21" s="35" t="s">
+      <c r="J22" s="11" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="37">
-        <v>20</v>
-      </c>
-      <c r="B22" s="38" t="s">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="4">
+        <v>21</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="C23" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="38" t="s">
+      <c r="D23" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="39" t="str">
-        <f t="shared" si="0"/>
-        <v>test20@dogs.com</v>
-      </c>
-      <c r="F22" s="38" t="s">
+      <c r="E23" s="29" t="str">
+        <f t="shared" si="1"/>
+        <v>test21@dogs.com</v>
+      </c>
+      <c r="F23" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G22" s="38" t="s">
+      <c r="G23" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="H22" s="40" t="s">
+      <c r="H23" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="I22" s="40" t="s">
+      <c r="I23" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="J22" s="41" t="s">
+      <c r="J23" s="12" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="E23" s="42"/>
-    </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="E24" s="42"/>
+      <c r="E24" s="31"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="E25" s="42"/>
+      <c r="E25" s="31"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="E26" s="42"/>
+      <c r="E26" s="31"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="E27" s="42"/>
+      <c r="E27" s="31"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="E28" s="42"/>
+      <c r="E28" s="31"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="E29" s="42"/>
+      <c r="E29" s="31"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="E30" s="42"/>
+      <c r="E30" s="31"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="E31" s="42"/>
+      <c r="E31" s="31"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="E32" s="42"/>
+      <c r="E32" s="31"/>
     </row>
     <row r="33" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E33" s="42"/>
+      <c r="E33" s="31"/>
     </row>
     <row r="34" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E34" s="42"/>
+      <c r="E34" s="31"/>
     </row>
     <row r="35" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E35" s="42"/>
+      <c r="E35" s="31"/>
     </row>
     <row r="36" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E36" s="42"/>
+      <c r="E36" s="31"/>
     </row>
     <row r="37" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E37" s="42"/>
+      <c r="E37" s="31"/>
     </row>
     <row r="38" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E38" s="42"/>
+      <c r="E38" s="31"/>
     </row>
     <row r="39" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E39" s="42"/>
+      <c r="E39" s="31"/>
     </row>
     <row r="40" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E40" s="42"/>
+      <c r="E40" s="31"/>
     </row>
     <row r="41" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E41" s="42"/>
+      <c r="E41" s="31"/>
+    </row>
+    <row r="42" spans="5:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="E42" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3688,21 +3786,25 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E23A5BC1-1A2C-4810-A079-76D1C51642AA}">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="43.9140625" customWidth="1"/>
+    <col min="3" max="3" width="36.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="23.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:3" ht="23.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="43" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3710,7 +3812,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3718,7 +3820,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3726,7 +3828,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3734,7 +3836,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3742,7 +3844,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3750,7 +3852,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3758,7 +3860,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3766,7 +3868,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3774,7 +3876,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3782,7 +3884,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3790,7 +3892,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3798,7 +3900,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3806,7 +3908,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3814,7 +3916,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3822,19 +3924,36 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="e" vm="16">
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C17" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="e" vm="17">
+      <c r="B18" t="e" vm="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C18" t="e" vm="19">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="e" vm="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C19" t="e" vm="21">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -3849,187 +3968,186 @@
   <dimension ref="A1:T13"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="27.58203125" style="32" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.6640625" style="32"/>
+    <col min="1" max="2" width="27.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="26" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:20" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="26" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="44" t="s">
+    <row r="2" spans="1:20" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="46">
+      <c r="C2" s="16">
         <v>1</v>
       </c>
-      <c r="D2" s="46">
+      <c r="D2" s="16">
         <v>2</v>
       </c>
-      <c r="E2" s="46">
+      <c r="E2" s="16">
         <v>3</v>
       </c>
-      <c r="F2" s="46">
+      <c r="F2" s="16">
         <v>4</v>
       </c>
-      <c r="G2" s="46">
+      <c r="G2" s="16">
         <v>5</v>
       </c>
-      <c r="H2" s="46">
+      <c r="H2" s="16">
         <v>6</v>
       </c>
-      <c r="I2" s="46">
+      <c r="I2" s="16">
         <v>7</v>
       </c>
-      <c r="J2" s="46">
+      <c r="J2" s="16">
         <v>8</v>
       </c>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="51"/>
-      <c r="P3" s="51"/>
-      <c r="Q3" s="51"/>
-      <c r="R3" s="51"/>
-      <c r="S3" s="51"/>
-      <c r="T3" s="51"/>
+      <c r="C3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="31"/>
-      <c r="B4" s="32" t="s">
+      <c r="A4" s="4"/>
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
-      <c r="M4" s="51"/>
-      <c r="N4" s="51"/>
-      <c r="O4" s="51"/>
-      <c r="P4" s="51"/>
-      <c r="Q4" s="51"/>
-      <c r="R4" s="51"/>
-      <c r="S4" s="51"/>
-      <c r="T4" s="51"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="31"/>
-      <c r="B5" s="32" t="s">
+      <c r="A5" s="4"/>
+      <c r="B5" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="35"/>
+      <c r="E5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="11"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="31"/>
-      <c r="B6" s="32" t="s">
+      <c r="A6" s="4"/>
+      <c r="B6" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="51"/>
-      <c r="J6" s="35"/>
+      <c r="F6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="5"/>
+      <c r="J6" s="11"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="31"/>
-      <c r="B7" s="32" t="s">
+      <c r="A7" s="4"/>
+      <c r="B7" t="s">
         <v>87</v>
       </c>
-      <c r="F7" s="51"/>
-      <c r="G7" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" s="35"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="11"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="31"/>
-      <c r="B8" s="32" t="s">
+      <c r="A8" s="4"/>
+      <c r="B8" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="35"/>
+      <c r="H8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="11"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="31"/>
-      <c r="B9" s="32" t="s">
+      <c r="A9" s="4"/>
+      <c r="B9" t="s">
         <v>8</v>
       </c>
-      <c r="I9" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="35"/>
+      <c r="I9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="11"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="37"/>
-      <c r="B10" s="38" t="s">
+      <c r="A10" s="7"/>
+      <c r="B10" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="53" t="s">
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="10" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="K11" s="51"/>
+      <c r="K11" s="5"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="L12" s="51"/>
+      <c r="L12" s="5"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="M13" s="51"/>
+      <c r="M13" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -4042,288 +4160,287 @@
   <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" style="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="32" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.25" style="32" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="51.75" style="32" customWidth="1"/>
-    <col min="5" max="5" width="53.83203125" style="34" customWidth="1"/>
-    <col min="6" max="6" width="54.1640625" style="32" customWidth="1"/>
-    <col min="7" max="7" width="33.58203125" style="32" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11" style="32" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.6640625" style="32"/>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="51.75" customWidth="1"/>
+    <col min="5" max="5" width="53.83203125" style="27" customWidth="1"/>
+    <col min="6" max="6" width="54.1640625" customWidth="1"/>
+    <col min="7" max="7" width="33.58203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="26" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="22"/>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23" t="s">
+    <row r="1" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="24"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="25"/>
-    </row>
-    <row r="2" spans="1:7" s="26" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="27" t="s">
+      <c r="E1" s="20"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="21"/>
+    </row>
+    <row r="2" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="28" t="s">
+      <c r="F2" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="G2" s="25" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="31">
+      <c r="A3" s="4">
         <v>1</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="34" t="s">
+      <c r="D3" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="F3" t="s">
         <v>108</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="G3" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="31">
+      <c r="A4" s="4">
         <v>2</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" t="s">
         <v>108</v>
       </c>
-      <c r="F4" s="32" t="s">
+      <c r="F4" t="s">
         <v>108</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="G4" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="31">
+      <c r="A5" s="4">
         <v>3</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" t="s">
         <v>75</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="D5" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" t="s">
         <v>58</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" t="s">
         <v>58</v>
       </c>
-      <c r="G5" s="35" t="s">
+      <c r="G5" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="31">
+      <c r="A6" s="4">
         <v>4</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="D6" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" t="s">
         <v>108</v>
       </c>
-      <c r="F6" s="32" t="s">
+      <c r="F6" t="s">
         <v>108</v>
       </c>
-      <c r="G6" s="35" t="s">
+      <c r="G6" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="31">
+      <c r="A7" s="4">
         <v>5</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" t="s">
         <v>88</v>
       </c>
-      <c r="D7" s="34" t="s">
+      <c r="D7" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" t="s">
         <v>108</v>
       </c>
-      <c r="F7" s="32" t="s">
+      <c r="F7" t="s">
         <v>108</v>
       </c>
-      <c r="G7" s="35" t="s">
+      <c r="G7" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="31">
+      <c r="A8" s="4">
         <v>6</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="34" t="s">
+      <c r="D8" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="E8" t="s">
         <v>81</v>
       </c>
-      <c r="F8" s="32" t="s">
+      <c r="F8" t="s">
         <v>81</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="31">
+      <c r="A9" s="4">
         <v>7</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" t="s">
         <v>75</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" t="s">
         <v>80</v>
       </c>
-      <c r="D9" s="34" t="s">
+      <c r="D9" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="E9" s="32" t="s">
+      <c r="E9" t="s">
         <v>82</v>
       </c>
-      <c r="F9" s="32" t="s">
+      <c r="F9" t="s">
         <v>82</v>
       </c>
-      <c r="G9" s="35" t="s">
+      <c r="G9" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="37">
+      <c r="A10" s="7">
         <v>8</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="40" t="s">
+      <c r="D10" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="38" t="s">
+      <c r="E10" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F10" s="38" t="s">
+      <c r="F10" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="G10" s="41" t="s">
+      <c r="G10" s="12" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="F11" s="34"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="F12" s="34"/>
+      <c r="F12" s="27"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="F13" s="34"/>
+      <c r="F13" s="27"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="F14" s="34"/>
+      <c r="F14" s="27"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="F15" s="34"/>
+      <c r="F15" s="27"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="E16" s="32"/>
+      <c r="E16"/>
     </row>
     <row r="17" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E17" s="32"/>
+      <c r="E17"/>
     </row>
     <row r="18" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E18" s="32"/>
+      <c r="E18"/>
     </row>
     <row r="19" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E19" s="32"/>
+      <c r="E19"/>
     </row>
     <row r="20" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E20" s="32"/>
+      <c r="E20"/>
     </row>
     <row r="21" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E21" s="32"/>
+      <c r="E21"/>
     </row>
     <row r="22" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E22" s="32"/>
+      <c r="E22"/>
     </row>
     <row r="23" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E23" s="32"/>
+      <c r="E23"/>
     </row>
     <row r="24" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E24" s="32"/>
+      <c r="E24"/>
     </row>
     <row r="25" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E25" s="32"/>
+      <c r="E25"/>
     </row>
     <row r="26" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E26" s="32"/>
+      <c r="E26"/>
     </row>
     <row r="27" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E27" s="32"/>
+      <c r="E27"/>
     </row>
     <row r="28" spans="5:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E28" s="32"/>
+      <c r="E28"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -4341,10 +4458,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -4352,7 +4469,7 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="e" vm="18">
+      <c r="B2" t="e" vm="22">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4360,7 +4477,7 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="e" vm="19">
+      <c r="B3" t="e" vm="23">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4368,7 +4485,7 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="e" vm="20">
+      <c r="B4" t="e" vm="24">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4376,7 +4493,7 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="e" vm="21">
+      <c r="B5" t="e" vm="25">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4384,7 +4501,7 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="e" vm="22">
+      <c r="B6" t="e" vm="26">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4392,7 +4509,7 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="e" vm="23">
+      <c r="B7" t="e" vm="27">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4400,7 +4517,7 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="e" vm="24">
+      <c r="B8" t="e" vm="28">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4408,7 +4525,7 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="e" vm="25">
+      <c r="B9" t="e" vm="29">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4443,7 +4560,7 @@
       <c r="D1" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="E1" s="33" t="s">
         <v>91</v>
       </c>
     </row>
@@ -4451,13 +4568,13 @@
       <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="55" t="s">
+      <c r="C2" t="s">
         <v>93</v>
       </c>
-      <c r="D2" s="55" t="s">
+      <c r="D2" t="s">
         <v>100</v>
       </c>
       <c r="E2" s="11" t="s">
@@ -4468,13 +4585,13 @@
       <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="C3" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="55" t="s">
+      <c r="D3" t="s">
         <v>100</v>
       </c>
       <c r="E3" s="11" t="s">
@@ -4485,13 +4602,13 @@
       <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="55" t="s">
+      <c r="B4" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="C4" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="55" t="s">
+      <c r="D4" t="s">
         <v>101</v>
       </c>
       <c r="E4" s="11" t="s">
@@ -4502,13 +4619,13 @@
       <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="55" t="s">
+      <c r="B5" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="55" t="s">
+      <c r="C5" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="55" t="s">
+      <c r="D5" t="s">
         <v>102</v>
       </c>
       <c r="E5" s="11" t="s">
@@ -4519,13 +4636,13 @@
       <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="55" t="s">
+      <c r="B6" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="55" t="s">
+      <c r="C6" t="s">
         <v>92</v>
       </c>
-      <c r="D6" s="55" t="s">
+      <c r="D6" t="s">
         <v>104</v>
       </c>
       <c r="E6" s="11" t="s">
@@ -4536,13 +4653,13 @@
       <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="55" t="s">
+      <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="55" t="s">
+      <c r="C7" t="s">
         <v>97</v>
       </c>
-      <c r="D7" s="55" t="s">
+      <c r="D7" t="s">
         <v>103</v>
       </c>
       <c r="E7" s="11" t="s">
@@ -4570,15 +4687,15 @@
       <c r="D10" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="E10" s="54" t="s">
+      <c r="E10" s="33" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="136" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="D11" s="7" t="e" vm="26">
+      <c r="D11" s="7" t="e" vm="30">
         <v>#VALUE!</v>
       </c>
-      <c r="E11" s="12" t="e" vm="27">
+      <c r="E11" s="12" t="e" vm="31">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4613,7 +4730,7 @@
       <c r="D1" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="E1" s="33" t="s">
         <v>91</v>
       </c>
     </row>
@@ -4621,13 +4738,13 @@
       <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="55" t="s">
+      <c r="C2" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="55" t="s">
+      <c r="D2" t="s">
         <v>100</v>
       </c>
       <c r="E2" s="11" t="s">
@@ -4655,15 +4772,15 @@
       <c r="D5" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="E5" s="54" t="s">
+      <c r="E5" s="33" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="179.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="D6" s="7" t="e" vm="28">
+      <c r="D6" s="7" t="e" vm="32">
         <v>#VALUE!</v>
       </c>
-      <c r="E6" s="12" t="e" vm="29">
+      <c r="E6" s="12" t="e" vm="33">
         <v>#VALUE!</v>
       </c>
     </row>
